--- a/Översikt ÅRE.xlsx
+++ b/Översikt ÅRE.xlsx
@@ -601,7 +601,7 @@
         <v>45932</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45184</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45847</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>46195</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>45580</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>44984</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46120</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>45895</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>46077</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44743</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44984</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>46108</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>46010</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45848</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45596</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45597</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45749</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>45813</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44998</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>45980</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45385</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>45572</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45804</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>46171</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45516</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>45697</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>45992</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>44883</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45688</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45572</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>44887</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>46077</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>45670</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>46010</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>45978</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>45874</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44843</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>44487</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45755</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>44510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>45755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>45565</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>45170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>46161</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44637</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>45688</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>45670</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>45572</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>46013</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44984</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>44778</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45754</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>45931</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>44946</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>45959</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>46057</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>46057</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44495</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>44894</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>45754</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45688</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45447</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>45980</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>45988</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         <v>45572</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45965</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>45895</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45485</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>45485</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45967</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45771</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45771</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44487</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45055</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45231</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45366</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45581</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>46010</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>45565</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>44729</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>44789</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>45151</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44701</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>44637</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>45167</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>44716</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>45645</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>45931</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>46007</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>46120</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>44964</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>45978</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>44889</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45835</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>45687</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44900</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>45975</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45614</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>45931</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>46007</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>46006</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45609</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44874</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>44984</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>45726</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44466</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>45006</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>44547</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45630</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>45965</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>46008</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45250</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45666</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>44487</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>45072</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>44904</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44487</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44690</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>44886</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>44904</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45072</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45366</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>45972</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>44680</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44487</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>44946</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>44781</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>46083</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45232</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45898</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>45985</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         <v>45835</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>44487</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>45351</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>45190</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>45264</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>44818</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>45575</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45740</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45072</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44570</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45688</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>45582</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45987</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45987</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45226</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>46054</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>46010</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>44781</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>44512</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>46048</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>46052</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>44883</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>46062</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45485</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>46119</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>44559</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44482</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>46136</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>46202</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>46056</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>44984</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>45749</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45813</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>45931</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45666</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45800</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>44532</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>44516</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>44686</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>44495</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>44812</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>44461</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44487</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>44841</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44515</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>44524</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44855</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>44502</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>44544</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44544</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44580</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>44487</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>44789</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44578</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>44700</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>44700</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44502</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>44538</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>44739</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>44536</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>44536</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>44719</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>44942</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>45518</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>45041</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>44550</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22249,7 +22249,7 @@
         <v>44909</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>44531</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>44984</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44719</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>45305</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>44529</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>44515</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>45621</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45576</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44908</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>44894</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
         <v>44998</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>45208</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>45246</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>45560</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45037</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>45639</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>45232</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23578,7 +23578,7 @@
         <v>44484</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>45583</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45296</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>45022</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45435</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
         <v>45586</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>44894</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45568</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>44998</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>44998</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>45281</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45595</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>45266</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24547,7 +24547,7 @@
         <v>45246</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>44510</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>45099</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>45548</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>44690</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>45263</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>45225</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>45600</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>44998</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45579</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45159</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>45257</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>45084</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>44903</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45149</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45134</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44960</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>44886</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>44948</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45596</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45219</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45219</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44935</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>44854</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>46139</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>44637</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>45232</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>44942</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>46139</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>44946</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>45231</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45085</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>44998</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>44998</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44998</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>44998</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>44889</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>45244</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45772</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45621</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45922</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>46001</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>44928</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>45915</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45996</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>45415</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45917</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45688</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>45575</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>45127</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         <v>46141</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>45714</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>45254</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>45559</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>44510</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>45616</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44896</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45931</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>45575</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>45435</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>45699</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>45614</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>45462</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>45925</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>45925</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>45463</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45159</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>46146</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>46147</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>45159</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>44631</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>45685</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>45695</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>44946</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45952</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>45560</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44498</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>45957</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45954</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>44482</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>45958</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>45958</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>45961</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45385</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>45218</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45961</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>44491</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30943,7 +30943,7 @@
         <v>45964</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45964</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>45965</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>44628</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         <v>45772</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>44917</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>45967</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>45560</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31527,7 +31527,7 @@
         <v>45401</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>45975</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31673,7 +31673,7 @@
         <v>45979</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>45091</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45091</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>44644</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>45979</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32043,7 +32043,7 @@
         <v>45548</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>45981</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>45980</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>45636</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         <v>45985</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>45987</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32486,7 +32486,7 @@
         <v>46156</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>45000</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>46161</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45989</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>45595</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>45992</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>44637</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>46161</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>45992</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>45917</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>44538</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>46160</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>45034</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>46160</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>44977</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33601,7 +33601,7 @@
         <v>45244</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>45995</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33752,7 +33752,7 @@
         <v>45999</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>45999</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>45401</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>45931</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>44552</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>45999</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34190,7 +34190,7 @@
         <v>45999</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         <v>44784</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34336,7 +34336,7 @@
         <v>46007</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         <v>46006</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>46006</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>46007</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>46007</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>46007</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>46009</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34852,7 +34852,7 @@
         <v>45518</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34925,7 +34925,7 @@
         <v>45548</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34998,7 +34998,7 @@
         <v>46058</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>44598</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35149,7 +35149,7 @@
         <v>45355</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>46070</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>45800</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35368,7 +35368,7 @@
         <v>46070</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>46070</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>45387</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35592,7 +35592,7 @@
         <v>46070</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>44706</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35738,7 +35738,7 @@
         <v>44781</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
         <v>46034</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>46036</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>44893</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36035,7 +36035,7 @@
         <v>44917</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36108,7 +36108,7 @@
         <v>46037</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36181,7 +36181,7 @@
         <v>45391</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36254,7 +36254,7 @@
         <v>45187</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36327,7 +36327,7 @@
         <v>46042</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>44970</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>45883</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>46048</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>46153</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45849</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>44905</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>46055</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>44830</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36999,7 +36999,7 @@
         <v>44874</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>45184</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>45126</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>46058</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>44496</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37374,7 +37374,7 @@
         <v>45604</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>45604</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45685</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37598,7 +37598,7 @@
         <v>45386</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>46066</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>45485</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>44967</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>45485</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37963,7 +37963,7 @@
         <v>46072</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>45568</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>45385</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>44803</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>45545</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45261</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>46079</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>46184</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45891</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45734</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>45947</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>45888</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>45891</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45736</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>45736</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39098,7 +39098,7 @@
         <v>44490</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>45888</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39244,7 +39244,7 @@
         <v>46189</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>46189</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45264</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>44946</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>44498</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39609,7 +39609,7 @@
         <v>45232</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39682,7 +39682,7 @@
         <v>44498</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39755,7 +39755,7 @@
         <v>46139</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39828,7 +39828,7 @@
         <v>46196</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>45583</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>44908</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>46196</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>46196</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>46196</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>45922</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40344,7 +40344,7 @@
         <v>45945</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>46147</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40490,7 +40490,7 @@
         <v>46147</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40563,7 +40563,7 @@
         <v>44930</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>45631</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>46202</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40782,7 +40782,7 @@
         <v>45616</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>45159</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>45150</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45714</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>46121</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>46128</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45303</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44496</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>44910</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44489</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>44893</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>46248</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41673,7 +41673,7 @@
         <v>45740</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45519</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41819,7 +41819,7 @@
         <v>44998</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>46206</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>45636</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42038,7 +42038,7 @@
         <v>46248</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42111,7 +42111,7 @@
         <v>45246</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42184,7 +42184,7 @@
         <v>46210</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42257,7 +42257,7 @@
         <v>44859</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>46210</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>44552</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>44936</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>45595</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45098</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>44834</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>44851</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>45254</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42919,7 +42919,7 @@
         <v>45439</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42992,7 +42992,7 @@
         <v>46258</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45560</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43138,7 +43138,7 @@
         <v>46262</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>46262</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43284,7 +43284,7 @@
         <v>45243</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43357,7 +43357,7 @@
         <v>44998</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>44540</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>46263</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43576,7 +43576,7 @@
         <v>45225</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>44946</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>45562</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43800,7 +43800,7 @@
         <v>44498</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>46267</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>45261</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44019,7 +44019,7 @@
         <v>44531</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>44911</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44165,7 +44165,7 @@
         <v>45786</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44238,7 +44238,7 @@
         <v>46268</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44311,7 +44311,7 @@
         <v>44998</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>46269</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>46255</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>46262</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>45779</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>46275</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44754,7 +44754,7 @@
         <v>45786</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45999</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>45898</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45968</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45061,7 +45061,7 @@
         <v>46279</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>46279</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45582</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45875</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45353,7 +45353,7 @@
         <v>45875</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45426,7 +45426,7 @@
         <v>45875</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45875</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45595</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>46237</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>46282</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>44495</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>46239</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>46237</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>46239</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>46239</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>46239</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45579</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>44958</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>45849</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46448,7 +46448,7 @@
         <v>45849</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46521,7 +46521,7 @@
         <v>45863</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45849</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45595</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46740,7 +46740,7 @@
         <v>45376</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45565</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46896,7 +46896,7 @@
         <v>45376</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>45565</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47047,7 +47047,7 @@
         <v>45006</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>45771</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>46000</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47276,7 +47276,7 @@
         <v>45595</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>46111</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>

--- a/Översikt ÅRE.xlsx
+++ b/Översikt ÅRE.xlsx
@@ -601,7 +601,7 @@
         <v>45932</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45184</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45847</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>46195</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44984</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>45580</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46120</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>45895</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>46077</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44743</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44984</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>46108</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>46010</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45848</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45596</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45597</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45749</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>45813</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44998</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>45980</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45572</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45385</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45804</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>46171</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45516</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>45697</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>45992</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>44883</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45572</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>45688</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>46077</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>44887</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>45670</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>46010</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>45978</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>45874</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44843</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>44487</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45755</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>44510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>45565</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45755</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>45170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>46161</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45572</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>44637</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44984</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45688</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45670</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>46013</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>44778</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45931</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>45754</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>44946</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>45959</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>46057</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>46057</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44495</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>45572</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>44894</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45688</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45754</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>45485</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>45485</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>45447</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>45980</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>45988</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45965</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>45895</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45967</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45771</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45771</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44487</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45581</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45231</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45366</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>46010</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45565</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>45055</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>44729</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>44889</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44637</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44701</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45645</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45931</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>46007</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>46120</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44789</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>45167</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44964</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45151</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>44716</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>45687</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44547</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>45250</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>45975</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>45931</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>46006</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>46007</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>44874</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44466</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44984</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>45609</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>46008</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45965</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45726</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>45614</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>44900</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45630</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45006</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45666</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>44487</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>44487</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44886</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>44487</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44781</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44680</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45366</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         <v>45972</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>44904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45835</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>44904</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>46083</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45232</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>45072</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44690</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45898</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45985</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>44946</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45072</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>44487</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44482</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>44883</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>44984</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>45740</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>46048</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45800</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>46052</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45688</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>46062</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45485</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>46119</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>46136</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>45575</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45582</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45190</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>45987</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>45987</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>46010</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>46054</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>44570</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44512</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45226</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44559</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>46202</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45072</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>45351</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>44818</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>46056</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>45931</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>45813</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>44781</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45666</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>46288</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45749</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45264</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44532</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44516</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>44686</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>44495</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>44812</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>44487</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>44841</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44515</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>44524</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>44855</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44502</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>44544</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44544</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44580</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44487</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44789</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>44578</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44700</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>44700</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>44502</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44538</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>44739</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>44536</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44536</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45355</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45232</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45127</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>44859</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45401</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>44893</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45772</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44529</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>45254</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44510</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>45281</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44834</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>44970</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>46058</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45261</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>46070</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>46070</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>46070</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>44495</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>46070</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>45387</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>44706</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45800</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45244</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>44889</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>46034</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45559</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>46036</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>44984</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>44886</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>46037</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>46042</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>45303</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>44911</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>44893</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>45545</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>44637</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>46048</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44490</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>44498</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>46055</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>46058</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45518</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45184</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45562</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45915</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45688</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45917</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>46066</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45740</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45485</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>45485</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45386</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>46072</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45576</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>46079</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>44538</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45888</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>45891</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45891</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45734</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>45736</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>45736</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45947</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45888</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>45931</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>45579</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>45586</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>45401</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45462</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>45925</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>45568</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>45925</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>45614</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>45463</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>45263</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>44910</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>46139</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         <v>45568</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>44637</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>45596</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         <v>46147</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45695</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>46147</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45952</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>44958</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>44942</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45954</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45958</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45958</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>44515</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45957</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>44491</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>45218</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>45964</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>45961</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>45583</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>45961</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45964</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45965</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45967</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44644</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>46128</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44998</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>45034</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>45975</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45979</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45979</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45980</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45435</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>45981</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>45159</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45159</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>44998</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>44998</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>45985</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>45519</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>45987</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45595</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>45084</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45992</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45000</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45992</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45989</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>45995</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>45999</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>45999</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>45999</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45999</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>46139</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>45931</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>44851</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>44498</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46006</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>46139</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>46006</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>46007</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>46007</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>46007</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>46007</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>46009</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>45922</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>44894</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32505,7 +32505,7 @@
         <v>45244</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>46141</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>44928</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45996</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>45714</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>44874</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>46001</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>44946</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>44946</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>46146</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>45232</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>46147</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45548</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>44482</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44803</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45518</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>44484</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>46156</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>46160</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>46160</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>45231</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>45134</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>46161</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45917</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>46161</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>44896</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>44498</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45099</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>44905</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>45849</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>45849</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44552</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>44510</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>44917</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45159</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45849</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45883</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45863</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45435</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>45604</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45254</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>46153</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45149</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>45604</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>44946</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35805,7 +35805,7 @@
         <v>44946</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>45595</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>45616</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>45849</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>46184</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>45022</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         <v>46189</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>46189</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>45699</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>45041</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>45232</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>44998</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>45575</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>44628</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36832,7 +36832,7 @@
         <v>45922</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36905,7 +36905,7 @@
         <v>45548</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>45037</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37056,7 +37056,7 @@
         <v>45945</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>46196</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>46196</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37275,7 +37275,7 @@
         <v>46196</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>46196</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>46121</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>44552</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>46202</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>45225</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>44998</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45621</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>44531</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46206</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>45560</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         <v>45560</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>45600</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>46210</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>45636</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>46210</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>45685</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>44598</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45583</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>45261</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>46258</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>44690</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44719</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>46262</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>46262</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45219</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39188,7 +39188,7 @@
         <v>45219</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>45150</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>45257</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>44854</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>46263</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39553,7 +39553,7 @@
         <v>45246</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>46268</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>44830</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>44935</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39850,7 +39850,7 @@
         <v>46267</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39923,7 +39923,7 @@
         <v>46262</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>46269</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45246</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>45786</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>46255</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>44998</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44998</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>45898</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>44781</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>44540</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>46275</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>44784</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45786</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>46279</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>46237</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45999</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45968</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>45208</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>45772</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>45636</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>46239</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>46239</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>46239</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>44489</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>46239</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>44998</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>46282</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>46237</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>44496</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>44909</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44960</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>44917</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45875</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>46288</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>46288</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45875</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>46288</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45875</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45579</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>46279</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>46289</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>44948</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>45091</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>45091</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43170,7 +43170,7 @@
         <v>46290</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         <v>46248</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45875</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>46248</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>46290</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>44496</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>44550</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>44498</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43759,7 +43759,7 @@
         <v>45225</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>44908</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>44908</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>45639</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>45391</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44129,7 +44129,7 @@
         <v>45243</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>45415</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>44977</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>44631</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>44719</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>44998</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45085</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>44894</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45385</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>44936</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45621</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>45548</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45714</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45595</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45098</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>45266</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>45126</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>44531</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45616</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>44942</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45439</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45575</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44903</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45159</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45246</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>44930</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45296</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45385</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>44967</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45187</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45305</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44998</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44998</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>45560</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>45560</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45685</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>45264</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45779</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>45582</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>45595</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47074,7 +47074,7 @@
         <v>45595</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45376</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45565</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>45376</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45565</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>45006</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>45771</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>46000</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>45595</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>46111</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>

--- a/Översikt ÅRE.xlsx
+++ b/Översikt ÅRE.xlsx
@@ -601,7 +601,7 @@
         <v>45932</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45184</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>45847</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>46195</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44984</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>45580</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46120</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>45895</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>46077</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44743</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44984</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>46108</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>46010</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45848</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45596</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45597</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45749</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>45813</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44998</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>45980</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45572</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45385</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45804</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>46171</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45516</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>45697</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>45992</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>44883</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>45572</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>45688</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>46077</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>44887</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>45670</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>46010</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>45978</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>45874</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44843</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>44487</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45755</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>44510</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>45565</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>45755</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>45170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>46161</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45572</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>44637</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>44984</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45688</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45670</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>46013</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>44778</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45931</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>45754</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>44946</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>45959</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>46057</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>45614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>46057</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44495</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>45572</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>44894</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         <v>45688</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45754</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>45485</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>45485</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>45447</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>45980</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>45988</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45965</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>45895</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45967</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45771</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45771</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44487</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45581</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45231</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45366</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>46010</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45565</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>45055</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>44729</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>44889</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44637</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44701</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>45645</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45931</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>46007</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>46120</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44789</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>45167</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44964</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45151</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>44716</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>45687</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44547</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>45250</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>45975</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>45931</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>46006</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>46007</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>44874</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44466</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44984</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>45609</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>46008</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45965</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45726</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>45614</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>44900</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45630</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45006</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45666</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>44487</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>44487</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44886</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>44487</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44781</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44680</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45366</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         <v>45972</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>44904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45835</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>44904</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>46083</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45232</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>45072</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44690</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45898</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45985</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>44946</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45072</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>44487</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44482</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>44883</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>44984</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>45740</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>46048</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45800</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>46052</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45688</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>46062</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45485</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>46119</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>46136</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>45575</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45582</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45190</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>45987</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>45987</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>46010</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>46054</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>44570</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>44512</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45226</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44559</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>46202</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45072</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>45351</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>44818</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>46056</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>45931</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>45813</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>44781</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45666</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>46288</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45749</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45264</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44532</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44516</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>44686</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>44495</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>44812</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>44487</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>44841</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44515</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>44524</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>44855</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44502</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>44544</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>44544</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44580</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44487</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>44789</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>44578</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44700</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>44700</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>44502</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>44538</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>44739</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>44536</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44536</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45355</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45232</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45127</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>44859</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45401</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>44893</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45772</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44529</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>45254</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44510</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>45281</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44834</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>44970</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>46058</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45261</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>46070</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>46070</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>46070</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>44495</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>46070</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>45387</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>44706</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45800</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45244</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>44889</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>46034</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45559</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>46036</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>44984</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>44886</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>46037</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>46042</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>45303</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>44911</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>44893</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>45545</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>44637</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>46048</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44490</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>44498</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>46055</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>46058</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45518</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45184</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45562</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45915</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45688</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45917</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>46066</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45740</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45485</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>45485</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45386</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>46072</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>45576</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>46079</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>44538</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45888</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>45891</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45891</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45734</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>45736</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>45736</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45947</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45888</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>45931</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>45579</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>45586</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>45401</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45462</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>45925</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>45568</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>45925</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>45614</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>45463</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>45263</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>44910</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>46139</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         <v>45568</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>44637</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>45596</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         <v>46147</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45695</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>46147</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45952</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>44958</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>44942</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45954</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45958</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45958</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>44515</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45957</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>44491</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>45218</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>45964</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>45961</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>45583</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>45961</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45964</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45965</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45967</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44644</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>46128</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44998</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>45034</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>45975</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45979</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45979</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45980</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45435</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>45981</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>45159</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45159</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>44998</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>44998</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>45985</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>45519</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>45987</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45595</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>45084</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45992</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45000</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45992</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45989</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>45995</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>45999</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>45999</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>45999</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45999</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>46139</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>45931</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>44851</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>44498</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46006</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>46139</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>46006</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31984,7 +31984,7 @@
         <v>46007</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>46007</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>46007</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>46007</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>46009</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>45922</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>44894</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32505,7 +32505,7 @@
         <v>45244</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         <v>46141</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>44928</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45996</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>45714</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>44874</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>46001</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>44946</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>44946</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>46146</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>45232</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>46147</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33386,7 +33386,7 @@
         <v>45548</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>44482</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>44803</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45518</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>44484</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>46156</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>46160</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33902,7 +33902,7 @@
         <v>46160</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>45231</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34053,7 +34053,7 @@
         <v>45134</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34126,7 +34126,7 @@
         <v>46161</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45917</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>46161</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>44896</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>44498</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45099</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>44905</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>45849</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>45849</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44552</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>44510</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>44917</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45159</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45849</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45883</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45863</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45435</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35367,7 +35367,7 @@
         <v>45604</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>45254</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35513,7 +35513,7 @@
         <v>46153</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45149</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35659,7 +35659,7 @@
         <v>45604</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>44946</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35805,7 +35805,7 @@
         <v>44946</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35878,7 +35878,7 @@
         <v>45595</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>45616</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>45849</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>46184</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>45022</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         <v>46189</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36316,7 +36316,7 @@
         <v>46189</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>45699</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>45041</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>45232</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>44998</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>45575</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>44628</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36832,7 +36832,7 @@
         <v>45922</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36905,7 +36905,7 @@
         <v>45548</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>45037</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37056,7 +37056,7 @@
         <v>45945</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>46196</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>46196</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37275,7 +37275,7 @@
         <v>46196</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>46196</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>46121</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>44552</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>46202</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>45225</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>44998</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>45621</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>44531</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46206</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>45560</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         <v>45560</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>45600</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>46210</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>45636</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>46210</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>45685</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>44598</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45583</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>45261</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>46258</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>44690</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44719</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38969,7 +38969,7 @@
         <v>46262</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39042,7 +39042,7 @@
         <v>46262</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45219</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39188,7 +39188,7 @@
         <v>45219</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>45150</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>45257</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>44854</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39480,7 +39480,7 @@
         <v>46263</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39553,7 +39553,7 @@
         <v>45246</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>46268</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>44830</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>44935</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39850,7 +39850,7 @@
         <v>46267</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39923,7 +39923,7 @@
         <v>46262</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>46269</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45246</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>45786</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>46255</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>44998</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44998</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>45898</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>44781</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>44540</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40663,7 +40663,7 @@
         <v>46275</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>44784</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45786</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>46279</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>46237</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45999</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45968</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>45208</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>45772</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>45636</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>46239</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>46239</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>46239</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>44489</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>46239</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>44998</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>46282</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>46237</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>44496</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>44909</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44960</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>44917</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45875</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>46288</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>46288</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45875</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>46288</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45875</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45579</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>46279</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>46289</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>44948</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>45091</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>45091</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43170,7 +43170,7 @@
         <v>46290</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43243,7 +43243,7 @@
         <v>46248</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45875</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>46248</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>46290</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>44496</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>44550</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>44498</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43759,7 +43759,7 @@
         <v>45225</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>44908</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>44908</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>45639</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>45391</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44129,7 +44129,7 @@
         <v>45243</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>45415</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>44977</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>44631</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>44719</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>44998</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45085</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>44894</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45385</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>44936</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45621</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>45548</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45714</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45595</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45098</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>45266</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
         <v>45126</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>44531</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45458,7 +45458,7 @@
         <v>45616</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>44942</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45439</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45677,7 +45677,7 @@
         <v>45575</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44903</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45159</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45246</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>44930</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46047,7 +46047,7 @@
         <v>45296</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>45385</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>44967</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46266,7 +46266,7 @@
         <v>45187</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45305</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44998</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>44998</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>45560</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>45560</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45685</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>45264</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45779</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>45582</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>45595</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47074,7 +47074,7 @@
         <v>45595</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45376</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45565</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>45376</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45565</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>45006</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47527,7 +47527,7 @@
         <v>45771</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>46000</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>45595</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>46111</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>

--- a/Översikt ÅRE.xlsx
+++ b/Översikt ÅRE.xlsx
@@ -601,7 +601,7 @@
         <v>45932</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45184</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>45847</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46195</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45580</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>44984</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>46120</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45895</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>46077</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44743</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>46108</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>46010</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44984</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45848</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>45597</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>45749</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45596</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>45813</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>44998</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>45980</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45572</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>45385</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45804</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>46171</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45516</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45697</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>44515</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45992</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>45572</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>45688</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44883</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>46077</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>44887</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45670</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>46010</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45978</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45874</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>44843</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>44487</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45755</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>45565</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44510</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>45755</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>45170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>46161</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>45572</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6470,7 +6470,7 @@
         <v>45688</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>45670</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44637</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>46013</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44984</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>44778</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>45931</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>45754</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>45959</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>46057</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>44946</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>46057</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>44495</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>44894</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>45572</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>45754</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>45688</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>45485</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>45485</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>45447</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>45980</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45988</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45965</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45895</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>45967</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>45771</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45771</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>44487</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>45581</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45055</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>45366</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>45231</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>46010</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>45565</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44729</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>46007</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44789</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44889</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>45151</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44701</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45931</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>45835</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>44637</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>45167</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>44716</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45645</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45978</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>44964</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>46120</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>45687</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>46007</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>46006</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>45250</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>45975</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>45931</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>44900</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45614</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>44984</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>45609</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>44874</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>45965</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>46008</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>45726</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>45006</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>44547</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>45630</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>45666</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>44487</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>45072</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>44904</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>45072</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44487</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44690</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>44886</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>45366</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>45972</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>44904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45835</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>46083</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>44680</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>44487</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45232</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>44946</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>44781</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45898</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45985</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>44487</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>45351</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>45190</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45072</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>46054</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>46010</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45264</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45740</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44818</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>46048</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17256,7 +17256,7 @@
         <v>45688</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45800</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>46052</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>46062</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45485</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>46119</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45582</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>46136</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45987</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45987</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>45575</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>44570</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45226</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>46202</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>44781</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44512</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44883</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>46056</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45931</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>45666</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>44559</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>44482</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>46288</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>45749</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>44984</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>44532</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>44516</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>44686</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>44495</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>44812</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44487</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44841</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>44515</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>44524</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>44855</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>44502</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>44544</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>44544</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>44580</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44487</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>44789</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>44578</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>44700</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44700</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>44502</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44538</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>44739</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>44536</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>44536</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>44719</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44942</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>44909</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45518</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>45041</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>44550</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45560</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>44531</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>44984</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>44719</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>44515</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>45576</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44529</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>44908</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45305</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45208</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44894</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45621</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>44484</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>45999</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>44998</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45246</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>44889</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45037</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>46007</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>46006</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>46006</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45582</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45639</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>46007</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>46007</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>46007</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>45232</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>46009</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>45583</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>45296</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>45022</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>46058</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>46070</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>45800</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>46070</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>46070</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45387</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>46070</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45595</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>44706</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>46034</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>46036</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45435</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>46037</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>46042</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45586</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44495</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>45915</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>46048</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45917</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45688</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>45159</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45084</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>44894</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>46055</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45568</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>45184</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>44998</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>44998</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>46058</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45595</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>45281</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45266</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>45931</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>45246</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45548</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45614</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>45462</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>45925</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45925</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45386</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>46066</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>45463</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>44510</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45099</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>45485</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>45263</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>44690</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45485</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>46072</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>45225</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         <v>45600</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>44998</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>45579</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>45579</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>46079</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>45695</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45952</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45891</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>45734</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>45947</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45888</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45891</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>45736</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45736</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>44958</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>45957</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29430,7 +29430,7 @@
         <v>45257</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29503,7 +29503,7 @@
         <v>45888</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>45954</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45958</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>44903</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45958</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45961</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45218</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45961</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>44491</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>45964</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>45964</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>45965</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>45149</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>45967</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45134</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>46139</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44886</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>45975</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>44960</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>44948</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45979</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>46147</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>46147</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>45979</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45981</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45980</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>45596</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>45985</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>45987</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>45219</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>45219</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45989</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>45992</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>45992</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44935</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32083,7 +32083,7 @@
         <v>45995</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
         <v>44854</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32229,7 +32229,7 @@
         <v>45999</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>45999</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>46128</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32448,7 +32448,7 @@
         <v>45931</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32521,7 +32521,7 @@
         <v>45999</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>44637</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45232</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>44942</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>44946</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45231</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>45085</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>44998</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>44998</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>44998</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>44998</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>45244</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33402,7 +33402,7 @@
         <v>45772</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45621</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>46139</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>45849</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>45849</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>45415</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>45575</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45127</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>45714</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>46139</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>45254</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34210,7 +34210,7 @@
         <v>45559</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>44510</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45616</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>44896</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45575</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>45435</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>45922</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>46001</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>45699</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45863</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45159</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44928</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45159</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>44631</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>45996</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>46141</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>45849</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>45685</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>44946</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>45560</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>44498</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>46146</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>46147</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45385</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>44482</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>44628</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45772</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36186,7 +36186,7 @@
         <v>44917</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36259,7 +36259,7 @@
         <v>46156</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>46161</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36405,7 +36405,7 @@
         <v>45560</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36478,7 +36478,7 @@
         <v>46161</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>45917</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36624,7 +36624,7 @@
         <v>46160</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>46160</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>45401</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>45091</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36926,7 +36926,7 @@
         <v>45091</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36999,7 +36999,7 @@
         <v>44644</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>45548</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>45636</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45000</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45595</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37374,7 +37374,7 @@
         <v>44637</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>45883</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>44538</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>46153</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>45849</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>45034</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>44977</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>45604</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37963,7 +37963,7 @@
         <v>45604</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>45244</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>46184</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>45401</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>46189</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>46189</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>44552</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>44784</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>45232</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38625,7 +38625,7 @@
         <v>46196</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>46196</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>46196</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38844,7 +38844,7 @@
         <v>46196</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38917,7 +38917,7 @@
         <v>45922</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38990,7 +38990,7 @@
         <v>45945</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39063,7 +39063,7 @@
         <v>45518</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>45548</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>46202</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>44598</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>46121</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>45355</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>44781</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>46206</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>44893</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>44917</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>46210</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>46210</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>45391</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45187</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>44970</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40163,7 +40163,7 @@
         <v>44905</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>46258</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>44830</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40387,7 +40387,7 @@
         <v>44874</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40460,7 +40460,7 @@
         <v>46262</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>46262</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40606,7 +40606,7 @@
         <v>45126</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>46263</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40757,7 +40757,7 @@
         <v>44496</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>45685</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>46267</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>44967</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41059,7 +41059,7 @@
         <v>45786</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>46268</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>45568</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>45385</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>46269</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>46262</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>44803</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>45545</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>45261</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>44490</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>46275</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>45786</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>45999</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42018,7 +42018,7 @@
         <v>45898</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>45968</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>46279</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>46237</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45264</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>44946</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>44498</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>46239</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42612,7 +42612,7 @@
         <v>44498</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>46237</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
         <v>46239</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>46239</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42904,7 +42904,7 @@
         <v>46239</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45583</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>44908</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>46282</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>44930</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>46288</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
         <v>45616</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>46279</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45159</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45150</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>46288</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>45714</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>46288</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>46248</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>46290</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>46290</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>46248</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>45875</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45875</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>45875</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45303</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>45875</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44530,7 +44530,7 @@
         <v>44496</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>46294</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>46294</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44754,7 +44754,7 @@
         <v>44910</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>46286</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
         <v>46289</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44973,7 +44973,7 @@
         <v>44489</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45046,7 +45046,7 @@
         <v>44893</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45124,7 +45124,7 @@
         <v>45740</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45197,7 +45197,7 @@
         <v>45519</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>44998</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45343,7 +45343,7 @@
         <v>46296</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>46255</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>46297</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>45636</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>45246</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>44859</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>44552</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>44936</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45595</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>45098</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>44834</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>44851</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46229,7 +46229,7 @@
         <v>45254</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>45439</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>45560</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46448,7 +46448,7 @@
         <v>45243</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46521,7 +46521,7 @@
         <v>44998</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>44540</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45225</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46740,7 +46740,7 @@
         <v>44946</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>45562</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46891,7 +46891,7 @@
         <v>44498</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>45261</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>44531</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>44911</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>44998</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47256,7 +47256,7 @@
         <v>45779</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45595</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45376</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45565</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45376</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>45565</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>45006</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45771</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47860,7 +47860,7 @@
         <v>46000</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>45595</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>46111</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>

--- a/Översikt ÅRE.xlsx
+++ b/Översikt ÅRE.xlsx
@@ -601,7 +601,7 @@
         <v>45932</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45184</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>45847</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46195</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45580</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>44984</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>46120</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45895</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>46077</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44743</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>44984</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46010</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>46108</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45596</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45848</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>45597</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>45749</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>45813</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>44998</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>45980</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45385</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>45572</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45804</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>46171</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45516</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>45697</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45992</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44883</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>44887</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>45688</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45572</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>46077</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45670</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>46010</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45978</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45874</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>44843</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>44487</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45755</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>46262</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44510</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>45755</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>45565</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>45170</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>46161</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>44637</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44984</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>45688</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45670</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45572</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>46013</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44778</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>44946</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         <v>45754</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>45931</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45959</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>46057</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>46057</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44495</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44894</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>45688</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45754</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45447</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45980</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45988</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>45572</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45485</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45485</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45965</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>45895</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>46290</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45967</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45771</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45771</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>44487</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>45055</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45231</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45366</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45581</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>46010</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>45565</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>44729</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>45151</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44716</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>44637</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>44789</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>44889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44701</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>45835</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45645</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>45167</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45931</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>46007</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44964</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>45978</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>46120</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45687</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>44900</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>45630</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>45006</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>44547</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>45609</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45250</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45975</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44874</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45931</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>46006</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>46007</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45614</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>44984</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45965</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>45726</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>46304</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>46008</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>45666</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44487</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>44904</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>44487</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45072</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>44904</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44886</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>44487</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44781</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>44680</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45366</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>44690</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45835</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45972</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>44946</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45072</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45232</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45898</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45985</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>46083</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>46262</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>44487</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>44482</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>44883</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>44512</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>45264</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>45072</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45740</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44984</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45688</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44559</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45800</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45351</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45575</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>45190</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>45582</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>44818</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>44570</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>44781</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45987</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45987</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>46010</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>46054</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>46048</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>46052</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>46062</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>45485</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>46119</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>46136</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45226</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>46202</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>46056</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>45931</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>45813</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45666</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>46288</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45749</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>44532</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>44516</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>44686</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>44495</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>44812</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44487</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>44841</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>44515</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44524</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>44855</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>44502</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>44544</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>44544</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>44578</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>44536</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>44536</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>44580</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>44502</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>44487</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>44538</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>44789</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>44700</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>44739</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>44700</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45355</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45232</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44631</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>44719</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>45232</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>44998</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44859</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>45085</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45548</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>45127</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44894</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44803</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>45518</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45385</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>44893</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>44936</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>45621</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45548</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>44484</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>45714</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45595</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>45098</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45401</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
         <v>45231</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45772</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>45134</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>45266</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>45126</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>44529</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>44896</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44531</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45616</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>45254</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44942</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>44498</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>45099</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44905</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>44510</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44552</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45281</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>44834</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44970</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>45439</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45575</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>44889</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45261</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44903</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>45159</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>44510</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>44917</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45246</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>44930</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45296</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45244</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45159</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45385</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45435</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44967</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>45187</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>45305</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>44998</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>44998</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45559</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45560</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45560</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>45685</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>44984</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>45254</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45303</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>44911</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45149</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>44893</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45545</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45264</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>44946</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>44946</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44637</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>44490</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45595</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>45779</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>45616</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>44498</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>45915</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45688</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45518</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45022</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>45917</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>45699</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>45041</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45740</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>45582</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>44998</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>45575</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>45576</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>44628</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>45595</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>45548</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45037</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>44538</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>44495</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45586</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>44552</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45931</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>45401</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45568</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45263</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>45462</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44910</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>45925</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45568</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45925</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45614</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45463</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>45225</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>44998</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45621</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>44637</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44531</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45579</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45596</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>45560</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45560</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>44958</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45600</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>44942</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45636</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>45685</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>44515</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45695</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>45583</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>44598</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>45583</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44644</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32068,7 +32068,7 @@
         <v>45261</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>45952</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45954</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45958</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>45958</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>45957</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44491</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>45218</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>44998</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45964</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>44690</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>45034</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45961</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45961</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>45964</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>44719</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45435</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45965</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45967</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45159</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>45159</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45219</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45219</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45150</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>44998</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44998</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45519</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>45595</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45084</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>45000</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45257</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>44854</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>45246</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45849</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45849</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44830</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44935</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>44851</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45863</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>45975</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>44498</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>45979</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>45979</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45246</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35300,7 +35300,7 @@
         <v>45849</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35373,7 +35373,7 @@
         <v>45980</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35446,7 +35446,7 @@
         <v>44998</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44998</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35592,7 +35592,7 @@
         <v>44781</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>44540</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35738,7 +35738,7 @@
         <v>45981</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
         <v>44784</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>44894</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45244</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45208</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45985</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>46147</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45772</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45636</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>46147</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45714</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>44489</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>44874</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>44998</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>45987</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>45992</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>45992</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>44946</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44946</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45989</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37213,7 +37213,7 @@
         <v>44496</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44909</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>45995</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>45999</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45999</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45999</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>45999</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45931</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>46128</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44960</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>44917</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>46006</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>46006</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>46007</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>45579</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>46007</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>46007</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>46007</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>44948</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>45091</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45091</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>46009</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>46058</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>44496</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>44550</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>46070</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>46070</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>46070</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>46070</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45387</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>44498</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>44706</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>46139</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>45225</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45800</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>46139</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>46034</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>44908</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>46036</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>46037</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>46042</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45922</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>44908</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>45639</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40460,7 +40460,7 @@
         <v>45391</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>46048</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>45243</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>45415</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40757,7 +40757,7 @@
         <v>44977</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>46141</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>44928</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45996</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>46055</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>46058</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41200,7 +41200,7 @@
         <v>45184</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>46001</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>46146</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>46066</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>46147</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>45485</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41638,7 +41638,7 @@
         <v>45485</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>44482</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>45386</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41857,7 +41857,7 @@
         <v>46072</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>46079</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>45888</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45891</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>45891</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>45734</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>45736</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45736</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>45947</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42544,7 +42544,7 @@
         <v>45888</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>46156</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>46160</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>46160</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>46139</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>46161</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45917</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43070,7 +43070,7 @@
         <v>46161</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>45849</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>45883</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>45604</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>46153</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43435,7 +43435,7 @@
         <v>45604</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>46184</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43581,7 +43581,7 @@
         <v>46189</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43654,7 +43654,7 @@
         <v>46189</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>45232</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43800,7 +43800,7 @@
         <v>45922</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>45945</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>46196</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44019,7 +44019,7 @@
         <v>46196</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>46196</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44165,7 +44165,7 @@
         <v>46196</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44238,7 +44238,7 @@
         <v>46121</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44311,7 +44311,7 @@
         <v>46202</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>46206</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>46210</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44530,7 +44530,7 @@
         <v>46210</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>46258</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>46263</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>46268</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>46267</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>46269</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>45786</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45898</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45119,7 +45119,7 @@
         <v>46275</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45786</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>46279</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45338,7 +45338,7 @@
         <v>46237</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45411,7 +45411,7 @@
         <v>45999</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45968</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>46239</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>46239</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>46239</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>46239</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>46282</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>46237</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>46288</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>46288</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>46288</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>46279</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>46290</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>46294</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>46248</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>45875</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>46248</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>46294</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>45875</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45875</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46891,7 +46891,7 @@
         <v>45875</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>46296</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>46297</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>46300</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>46255</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>46286</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>46289</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>46300</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>46302</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>46300</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>46304</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>46302</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>46262</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>45595</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45376</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>45565</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48074,7 +48074,7 @@
         <v>45376</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45565</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48225,7 +48225,7 @@
         <v>45006</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>45771</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>46000</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>45595</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48527,7 +48527,7 @@
         <v>46111</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>

--- a/Översikt ÅRE.xlsx
+++ b/Översikt ÅRE.xlsx
@@ -601,7 +601,7 @@
         <v>45932</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45184</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>45847</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46195</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45580</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>44984</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>46120</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45895</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>46077</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44743</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>44984</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46010</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>46108</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45596</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45848</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>45597</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>45749</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>45813</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>44998</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>45980</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45385</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>45572</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45804</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>46171</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45516</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>45697</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45992</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44883</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>44887</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>45688</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45572</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>46077</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45670</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>46010</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45978</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45874</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>44843</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>44487</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45755</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>46262</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44510</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>45755</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>45565</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>45170</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>46161</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>44637</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44984</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>45688</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45670</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45572</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>46013</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44778</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>44946</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         <v>45754</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>45931</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45959</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>46057</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>46057</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44495</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44894</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>45688</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45754</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45447</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45980</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45988</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>45572</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45485</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45485</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45965</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>45895</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>46290</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45967</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45771</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45771</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>44487</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>45055</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45231</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45366</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45581</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>46010</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>45565</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>44729</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>45151</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44716</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>44637</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>44789</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>44889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44701</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>45835</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45645</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>45167</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45931</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>46007</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44964</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>45978</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>46120</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45687</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>44900</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>45630</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>45006</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>44547</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>45609</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45250</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45975</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44874</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45931</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>46006</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>46007</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45614</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>44984</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45965</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>45726</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>46304</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>46008</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>45666</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44487</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>44904</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>44487</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45072</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>44904</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44886</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>44487</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44781</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>44680</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45366</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>44690</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45835</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45972</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>44946</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45072</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45232</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45898</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45985</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>46083</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>46262</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>44487</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>44482</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>44883</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>44512</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>45264</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>45072</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45740</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44984</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45688</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44559</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45800</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45351</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45575</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>45190</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>45582</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>44818</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>44570</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>44781</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45987</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45987</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>46010</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>46054</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>46048</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>46052</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>46062</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>45485</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>46119</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>46136</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45226</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>46202</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>46056</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>45931</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>45813</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45666</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>46288</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45749</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>44532</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>44516</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>44686</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20716,7 +20716,7 @@
         <v>44495</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>44812</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>44487</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>44841</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>44515</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>44524</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>44855</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>44502</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21300,7 +21300,7 @@
         <v>44544</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>44544</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>44578</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>44536</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>44536</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>44580</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>44502</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>44487</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>44538</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>44789</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         <v>44700</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>44739</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>44700</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45355</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>45232</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>44631</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>44719</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>45232</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>44998</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44859</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>45085</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45548</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>45127</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44894</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>44803</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>45518</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45385</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>44893</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>44936</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>45621</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45548</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>44484</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>45714</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45595</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>45098</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45401</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
         <v>45231</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45772</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>45134</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>45266</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>45126</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>44529</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>44896</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44531</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45616</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>45254</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44942</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>44498</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>45099</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44905</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>44510</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44552</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45281</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>44834</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44970</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>45439</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45575</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>44889</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45261</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44903</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>45159</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>44510</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>44917</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>45246</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>44930</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45296</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45244</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45159</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45385</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45435</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44967</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>45187</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>45305</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>44998</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>44998</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45559</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45560</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45560</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>45685</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>44984</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>45254</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45303</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>44911</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45149</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>44893</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45545</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45264</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>44946</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>44946</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44637</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>44490</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45595</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>45779</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>45616</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>44498</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>45915</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45688</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45518</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45022</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>45917</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>45699</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>45041</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45740</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>45582</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>44998</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>45575</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>45576</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>44628</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>45595</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>45548</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45037</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>44538</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>44495</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45586</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>44552</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45931</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>45401</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45568</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45263</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>45462</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44910</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>45925</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45568</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45925</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45614</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45463</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>45225</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>44998</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45621</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>44637</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44531</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45579</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45596</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>45560</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45560</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>44958</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45600</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>44942</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45636</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31537,7 +31537,7 @@
         <v>45685</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>44515</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45695</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>45583</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>44598</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>45583</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44644</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32068,7 +32068,7 @@
         <v>45261</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>45952</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45954</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45958</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>45958</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>45957</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>44491</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>45218</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>44998</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45964</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>44690</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>45034</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45961</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45961</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>45964</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>44719</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45435</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>45965</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>45967</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45159</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>45159</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45219</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45219</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45150</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>44998</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44998</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45519</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>45595</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45084</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>45000</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45257</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>44854</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>45246</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45849</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45849</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44830</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44935</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>44851</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45863</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>45975</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>44498</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>45979</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>45979</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45246</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35300,7 +35300,7 @@
         <v>45849</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35373,7 +35373,7 @@
         <v>45980</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35446,7 +35446,7 @@
         <v>44998</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>44998</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35592,7 +35592,7 @@
         <v>44781</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>44540</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35738,7 +35738,7 @@
         <v>45981</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
         <v>44784</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>44894</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45244</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45208</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45985</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>46147</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45772</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45636</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>46147</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45714</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>44489</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>44874</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>44998</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>45987</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>45992</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36921,7 +36921,7 @@
         <v>45992</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>44946</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44946</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>45989</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37213,7 +37213,7 @@
         <v>44496</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>44909</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>45995</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>45999</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45999</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45999</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>45999</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45931</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>46128</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44960</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37948,7 +37948,7 @@
         <v>44917</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>46006</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>46006</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>46007</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38240,7 +38240,7 @@
         <v>45579</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>46007</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>46007</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>46007</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>44948</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>45091</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45091</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>46009</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>46058</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>44496</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>44550</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>46070</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>46070</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>46070</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>46070</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45387</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>44498</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>44706</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>46139</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>45225</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45800</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>46139</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>46034</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>44908</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>46036</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>46037</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>46042</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45922</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>44908</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>45639</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40460,7 +40460,7 @@
         <v>45391</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40533,7 +40533,7 @@
         <v>46048</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>45243</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>45415</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40757,7 +40757,7 @@
         <v>44977</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>46141</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>44928</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45996</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>46055</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>46058</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41200,7 +41200,7 @@
         <v>45184</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>46001</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>46146</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>46066</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>46147</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>45485</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41638,7 +41638,7 @@
         <v>45485</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>44482</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>45386</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41857,7 +41857,7 @@
         <v>46072</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>46079</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>45888</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45891</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>45891</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>45734</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>45736</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45736</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>45947</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42544,7 +42544,7 @@
         <v>45888</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>46156</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>46160</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>46160</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>46139</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>46161</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45917</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43070,7 +43070,7 @@
         <v>46161</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>45849</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>45883</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>45604</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>46153</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43435,7 +43435,7 @@
         <v>45604</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>46184</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43581,7 +43581,7 @@
         <v>46189</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43654,7 +43654,7 @@
         <v>46189</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>45232</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43800,7 +43800,7 @@
         <v>45922</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>45945</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43946,7 +43946,7 @@
         <v>46196</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44019,7 +44019,7 @@
         <v>46196</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>46196</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44165,7 +44165,7 @@
         <v>46196</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44238,7 +44238,7 @@
         <v>46121</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44311,7 +44311,7 @@
         <v>46202</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>46206</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>46210</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44530,7 +44530,7 @@
         <v>46210</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>46258</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>46263</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>46268</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>46267</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>46269</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>45786</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45898</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45119,7 +45119,7 @@
         <v>46275</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>45786</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>46279</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45338,7 +45338,7 @@
         <v>46237</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45411,7 +45411,7 @@
         <v>45999</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45968</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>46239</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>46239</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>46239</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>46239</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>46282</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>46237</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>46288</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>46288</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>46288</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>46279</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>46290</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>46294</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>46248</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>45875</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>46248</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>46294</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>45875</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46818,7 +46818,7 @@
         <v>45875</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46891,7 +46891,7 @@
         <v>45875</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>46296</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>46297</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>46300</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>46255</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>46286</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>46289</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>46300</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>46302</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47553,7 +47553,7 @@
         <v>46300</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47626,7 +47626,7 @@
         <v>46304</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>46302</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47772,7 +47772,7 @@
         <v>46262</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>45595</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45376</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47996,7 +47996,7 @@
         <v>45565</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48074,7 +48074,7 @@
         <v>45376</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45565</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48225,7 +48225,7 @@
         <v>45006</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>45771</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48376,7 +48376,7 @@
         <v>46000</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>45595</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48527,7 +48527,7 @@
         <v>46111</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>

--- a/Översikt ÅRE.xlsx
+++ b/Översikt ÅRE.xlsx
@@ -601,7 +601,7 @@
         <v>45932</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45184</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>45847</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46195</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45580</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         <v>44984</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>46120</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45895</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>46077</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44743</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>44984</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46108</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>46010</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45848</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>45597</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>45596</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>45749</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>45813</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>44998</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>45980</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45385</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>45572</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45804</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>46171</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44515</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>45516</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>45697</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45992</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44883</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>45688</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>45572</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44887</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>46077</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45670</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>45749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>46010</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45978</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45874</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>44843</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>44487</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45755</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>46262</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44510</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>45755</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>45565</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>45170</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>46161</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         <v>44637</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>45688</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>45670</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45572</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>44984</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>46013</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>44778</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>45754</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>45931</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>44946</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>46057</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>45959</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>46057</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44495</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44894</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>45754</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45688</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45447</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45980</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>45988</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>45965</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>45572</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>45485</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>45485</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>46290</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45967</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45771</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45771</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>44487</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>45055</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45231</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45366</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45581</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>46010</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>45565</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>44729</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>44789</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45151</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>44701</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44637</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>45167</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>44716</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>45645</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>45931</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>46007</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44964</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>45978</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>46120</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>44889</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>45835</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45687</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>44900</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>45975</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>45614</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45931</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>46007</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>46006</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>44984</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45609</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>44874</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>45006</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>44547</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45630</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>46008</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>46304</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>45726</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45250</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14223,7 +14223,7 @@
         <v>45965</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>45666</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44487</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>45072</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>44904</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>44487</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>44690</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44886</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>44904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>45072</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>45366</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45972</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44680</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>44487</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>44946</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>45232</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>44781</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>45898</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>46083</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>46262</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>45985</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45835</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>44487</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45351</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45190</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>45264</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44818</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>45740</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45072</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45575</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45688</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>44570</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45582</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>45226</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45987</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45987</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>46054</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>46010</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>46048</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>46052</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46062</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45485</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>46119</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44781</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44512</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>46136</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>44883</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>46202</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>44559</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>46056</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45813</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>45931</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45666</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>46288</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>44984</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>45749</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>45800</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>44532</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44516</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>44686</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>44495</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>44812</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>44487</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         <v>44841</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>44515</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>44524</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>44855</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>44502</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>44544</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>44544</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>44580</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>44487</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44789</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>44578</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>44700</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44700</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>44502</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>44538</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>44739</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>44536</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>44536</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44909</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>44719</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>44942</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>45518</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>45560</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45041</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>44550</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>44531</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>44984</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>44719</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>44529</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>45305</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>44515</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>45621</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>45576</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>44908</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>44894</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>44998</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>45208</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>45037</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45639</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45232</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>45583</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
         <v>45296</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>45022</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>45435</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -24068,7 +24068,7 @@
         <v>45586</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>45246</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>44894</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>45159</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>45084</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         <v>45281</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>45568</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45595</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>45266</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44998</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>44998</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>45246</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>44510</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>45548</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>45099</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>44690</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45263</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>45225</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45600</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>44998</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45579</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45257</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>44903</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45149</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45134</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>44960</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>44948</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45596</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45219</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>45219</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>46139</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>44935</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>44854</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>46139</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>44637</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>45232</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>44889</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>45922</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>46001</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>44942</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>44928</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -27091,7 +27091,7 @@
         <v>45996</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>46141</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>44946</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>45231</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45085</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>44998</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>44998</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44998</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>44998</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>45915</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>45917</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>45688</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>45244</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>46146</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45772</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>46147</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45621</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45415</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45931</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>45614</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45462</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45575</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>45127</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>45925</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45925</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>45463</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>45714</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>45254</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>45559</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>44510</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45616</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>44896</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45575</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>45435</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>45699</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45695</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>45952</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45957</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>45159</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>45954</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         <v>45958</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -30099,7 +30099,7 @@
         <v>45958</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>46156</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45961</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>45159</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>46161</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>45218</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>44631</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30610,7 +30610,7 @@
         <v>45961</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>44491</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45964</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45964</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>45965</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>46161</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>45685</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>45917</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>46160</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>45967</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>46160</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>44946</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>45560</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>44498</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>45975</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45979</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>45979</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45981</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>45385</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45980</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45985</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>44628</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>45987</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         <v>45772</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32387,7 +32387,7 @@
         <v>44917</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>45989</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32533,7 +32533,7 @@
         <v>45560</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>45992</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>45992</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>45401</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45995</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>45999</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32971,7 +32971,7 @@
         <v>45999</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>45091</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45091</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>44644</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>45931</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>45999</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45548</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45999</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45636</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>46007</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>46006</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>46006</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>46007</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33925,7 +33925,7 @@
         <v>46007</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>46007</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>45000</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>46009</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45595</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>44637</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>44538</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>45034</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>44977</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34597,7 +34597,7 @@
         <v>46058</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45244</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>46070</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>45800</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45883</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34972,7 +34972,7 @@
         <v>46070</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>46070</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35123,7 +35123,7 @@
         <v>45387</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35196,7 +35196,7 @@
         <v>46070</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>44706</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>45401</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>44552</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>46034</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35561,7 +35561,7 @@
         <v>46153</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45849</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         <v>46036</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>46037</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>46042</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45604</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>45604</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44784</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>46048</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>46055</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45184</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45518</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>45548</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>46058</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>46184</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45386</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>46066</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>44598</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45485</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>45355</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>46189</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37104,7 +37104,7 @@
         <v>46189</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37177,7 +37177,7 @@
         <v>45485</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37250,7 +37250,7 @@
         <v>46072</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>44781</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>46079</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37474,7 +37474,7 @@
         <v>45891</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45734</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37625,7 +37625,7 @@
         <v>45947</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45888</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>45891</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37859,7 +37859,7 @@
         <v>45736</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>45736</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>45888</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44893</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38166,7 +38166,7 @@
         <v>44917</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>45391</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>45187</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>45232</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>46139</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>44970</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>46196</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>44905</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>46196</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>46196</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>44830</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38974,7 +38974,7 @@
         <v>44874</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -39047,7 +39047,7 @@
         <v>46147</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>46196</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>46147</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
         <v>45126</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>44496</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>46202</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>45685</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>44967</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>46121</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45568</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45385</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>46128</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>44803</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>45545</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>45261</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>44490</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>46206</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>45264</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44946</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>44498</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44498</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>46210</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>46210</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>45583</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>44908</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>46258</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>44930</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45616</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>45159</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45150</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>45786</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>45714</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>46275</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45786</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41554,7 +41554,7 @@
         <v>45999</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45898</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>46279</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45303</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44496</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>44910</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>46237</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>44489</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42158,7 +42158,7 @@
         <v>44893</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>46239</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>46237</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>46239</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>46239</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42528,7 +42528,7 @@
         <v>46239</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>45740</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>45519</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>44998</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42820,7 +42820,7 @@
         <v>45636</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45246</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42966,7 +42966,7 @@
         <v>46282</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         <v>44859</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>44552</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44936</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43258,7 +43258,7 @@
         <v>46288</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43336,7 +43336,7 @@
         <v>46279</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>46288</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>46288</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45595</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43633,7 +43633,7 @@
         <v>46248</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45098</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>44834</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>46290</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>44851</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>46248</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>45254</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>45439</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>45560</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>45243</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>44998</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>44540</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45225</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>44946</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>46294</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44733,7 +44733,7 @@
         <v>46294</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>46286</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>46289</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>44498</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45261</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>44531</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>46296</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>46255</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45322,7 +45322,7 @@
         <v>46297</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>44911</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45468,7 +45468,7 @@
         <v>44998</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>45779</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>46300</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>46300</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>46300</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>46302</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45582</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>46302</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45595</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46125,7 +46125,7 @@
         <v>46262</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>46304</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46271,7 +46271,7 @@
         <v>44495</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>46263</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46417,7 +46417,7 @@
         <v>46307</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>45875</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45875</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45875</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46714,7 +46714,7 @@
         <v>45875</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46787,7 +46787,7 @@
         <v>45922</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46860,7 +46860,7 @@
         <v>46308</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46933,7 +46933,7 @@
         <v>46268</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>45579</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45945</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>44958</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>46310</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>46269</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>45968</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>46311</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>46267</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47595,7 +47595,7 @@
         <v>45849</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45849</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47741,7 +47741,7 @@
         <v>45863</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45849</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>45595</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45376</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -48038,7 +48038,7 @@
         <v>45565</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>45376</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45565</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -48267,7 +48267,7 @@
         <v>45006</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48340,7 +48340,7 @@
         <v>45771</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>46000</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45595</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>46111</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>

--- a/Översikt ÅRE.xlsx
+++ b/Översikt ÅRE.xlsx
@@ -601,7 +601,7 @@
         <v>45932</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45184</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>45847</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46195</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44984</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>45580</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>46120</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46077</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>45895</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44743</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>44984</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46108</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>46010</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45597</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>45848</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>45749</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45596</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>46315</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>45813</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>44998</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>45980</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45385</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45804</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>46171</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45572</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>45516</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45697</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>44515</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45992</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44883</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>45688</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44887</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>45572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>46077</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>45670</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>45749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>46010</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45978</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>45874</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44843</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>45755</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>46262</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>44510</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>45170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>46161</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>45565</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>45688</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>45670</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>45572</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>46288</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44637</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>44984</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>46013</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44778</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>45754</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45931</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>45959</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>44946</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>46057</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44495</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>45688</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>45754</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45965</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>45447</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45980</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>45988</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45572</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>46290</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>45485</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>45485</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44894</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45967</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>46317</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45771</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45771</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>45366</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45055</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>46010</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>45581</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>45565</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45231</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>44729</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>44964</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>45151</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44716</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>45978</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>45931</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>46007</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44889</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>45835</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>46120</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>44637</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>44701</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45645</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44789</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>45167</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>45687</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>45614</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>44900</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>44984</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45630</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45006</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45975</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45931</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>46006</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>46007</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>45250</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>46304</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>45726</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>44547</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45965</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>46008</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>44874</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>45609</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45666</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>44946</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>45072</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45366</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>45232</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45972</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>45898</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44886</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45835</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>46083</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45072</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>46262</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>45985</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44781</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>44680</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>44904</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>44904</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>44690</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45740</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44883</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45226</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45688</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45582</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45264</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>46202</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>45987</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45987</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>46056</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45931</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45813</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>45666</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>46010</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>46054</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>46048</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>45800</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>46052</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>46062</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45485</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>46119</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>46136</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>44984</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45749</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45072</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>46314</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45575</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45190</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>44570</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44512</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>44559</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45351</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44818</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44781</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>44532</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>44516</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44686</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>44495</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44812</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>44841</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>44515</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44524</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44855</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>44502</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44544</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44544</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44580</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>44789</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>44578</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>44700</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>44700</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>44502</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44538</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44739</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>44536</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44536</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45579</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44948</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>45091</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>45091</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>45355</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>44496</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>44889</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45232</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44550</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>44498</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>45225</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>46161</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45917</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>46161</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>45915</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>44908</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>44859</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45688</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45917</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>44908</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45639</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>45127</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45391</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45931</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45243</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>45462</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45849</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45883</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45415</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45925</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45925</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45614</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45463</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>44977</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>44631</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44719</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>44998</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44893</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45085</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>45604</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>46153</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45401</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>45604</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>45772</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44529</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>44894</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45254</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>45385</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>44936</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45621</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>45695</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>45548</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>45714</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45952</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45954</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45595</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>45098</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45958</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>45958</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45957</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45218</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>45266</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>45126</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>46184</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>45964</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>45961</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45961</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>45964</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>44531</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>46189</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>46189</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45616</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44942</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45965</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45967</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45232</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>46196</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>46196</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>46196</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>46196</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45439</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45575</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>46121</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>45975</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>44510</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44903</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45979</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>45979</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>45980</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>45159</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>46202</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>45246</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44930</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45296</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45981</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>45281</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>45385</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>45985</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>44967</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>45187</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>45305</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>44998</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44998</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44834</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>45560</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45560</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>46206</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>45987</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45685</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44970</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>46210</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29772,7 +29772,7 @@
         <v>45992</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45992</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>46210</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>45989</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45995</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>45999</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>45264</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>46258</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45999</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45999</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45999</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>45931</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>46006</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45779</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>45786</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>46006</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>46007</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>46007</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45898</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>46007</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>46007</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45786</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45261</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>46279</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>46009</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>46237</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46058</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46239</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>46239</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>46239</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>46070</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>46070</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>46070</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>46070</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45387</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>44706</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>46239</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>45800</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>45582</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>46282</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32712,7 +32712,7 @@
         <v>46034</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>45595</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>46036</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32931,7 +32931,7 @@
         <v>46237</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>46037</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>44495</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
         <v>46042</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>46288</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>46288</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>46048</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>46288</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33535,7 +33535,7 @@
         <v>46279</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>46055</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>46058</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45579</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>46290</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45184</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>46294</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>46248</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>44958</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>46066</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>46248</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>46294</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>45485</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>45485</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>45386</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>46072</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>45244</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>46296</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34859,7 +34859,7 @@
         <v>46079</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>45888</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45891</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>45891</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45734</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>45736</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45736</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>45947</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>45888</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>46297</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>46300</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>46255</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>46139</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>46286</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>46289</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>46300</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>46147</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>46302</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>46147</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>45559</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>45849</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>45849</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>46300</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>44984</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45863</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>46304</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>46302</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>45849</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>46128</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45875</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45875</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45875</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45875</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>45303</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>44911</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>46307</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>44893</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45545</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>46308</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44637</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>44498</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>45945</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>46267</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>45922</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>45968</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>45518</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>46310</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>46268</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>46311</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>46139</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>46139</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>45740</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>46263</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>46269</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>46314</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>46314</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>46314</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45922</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39148,7 +39148,7 @@
         <v>45576</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>45999</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>44538</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>46262</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>45586</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>46141</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44928</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>45401</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>45996</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45568</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45263</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>46001</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>44910</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>46146</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>46275</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45568</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>46147</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>44637</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40477,7 +40477,7 @@
         <v>45596</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44942</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>46156</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>46160</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>44515</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>46160</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45583</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44644</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>44998</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45034</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45435</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>45159</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45159</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>44998</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>44998</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>45519</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>45595</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41743,7 +41743,7 @@
         <v>45084</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41816,7 +41816,7 @@
         <v>45000</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>44851</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>44498</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>44894</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>45244</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>45714</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>44874</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>44946</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>44946</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45232</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>45548</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42634,7 +42634,7 @@
         <v>44803</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
         <v>45518</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45231</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45134</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42926,7 +42926,7 @@
         <v>44896</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>44498</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43072,7 +43072,7 @@
         <v>45099</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>44905</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>44552</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>44510</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>44917</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>45159</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45435</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>45254</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45149</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44946</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44946</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45595</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45616</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45022</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45699</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45041</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>44998</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45575</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>44628</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44464,7 +44464,7 @@
         <v>45548</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45037</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>44552</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44688,7 +44688,7 @@
         <v>45225</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>44998</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45621</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44912,7 +44912,7 @@
         <v>44531</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44985,7 +44985,7 @@
         <v>45560</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45058,7 +45058,7 @@
         <v>45560</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>45600</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>45636</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45685</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>44598</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>45583</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>45261</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44690</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>44719</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45219</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45219</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>45150</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45944,7 +45944,7 @@
         <v>45257</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>44854</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46090,7 +46090,7 @@
         <v>45246</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46163,7 +46163,7 @@
         <v>44830</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>44935</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45246</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>44998</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>44998</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>44781</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>44540</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>44784</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46752,7 +46752,7 @@
         <v>45208</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>45772</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45636</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>44998</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>44496</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>44909</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>44960</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>44917</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47341,7 +47341,7 @@
         <v>45595</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>45376</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>45565</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45376</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45565</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>45006</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>45771</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47872,7 +47872,7 @@
         <v>46000</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>45595</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>46111</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>

--- a/Översikt ÅRE.xlsx
+++ b/Översikt ÅRE.xlsx
@@ -601,7 +601,7 @@
         <v>45932</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>45184</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>45847</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46195</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44984</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>45580</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>46120</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46077</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>45895</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44743</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>44984</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46108</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>46010</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>45597</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>45848</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>45749</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>45596</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>46315</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>45813</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>44998</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>45980</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45385</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45804</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>46171</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45572</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>45516</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45697</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         <v>44515</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45992</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44883</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>45688</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44887</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>45572</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>46077</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>45670</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>45749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>46010</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45978</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>45874</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44843</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>45755</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>46262</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>45755</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>44510</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>45170</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>46161</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>45565</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>45688</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>45670</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>45572</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>46288</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44637</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>44984</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>46013</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44778</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>45754</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45931</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>45959</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>44946</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>46057</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44495</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>45688</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>45754</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45965</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>45447</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45895</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45980</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         <v>45988</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45572</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>46290</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>45485</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>45485</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44894</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45967</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>46317</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45771</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45771</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>45366</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45055</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>46010</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>45581</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>45565</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45231</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>44729</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>44964</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>45151</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44716</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>45978</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>45931</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>46007</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44889</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>45835</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>46120</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>44637</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>44701</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45645</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44789</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>45167</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>45687</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>45614</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>44900</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>44984</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45630</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45006</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45975</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45931</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>46006</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>46007</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>45250</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>46304</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>45726</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>44547</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45965</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>46008</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>44874</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>45609</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45666</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>44946</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>45072</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45366</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>45232</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45972</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         <v>45898</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44886</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45835</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>46083</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45072</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>46262</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>45985</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44781</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>44680</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>44904</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>44904</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>44690</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45740</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44883</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45226</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45688</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45582</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45264</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>46202</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>45987</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45987</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>46056</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45931</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45813</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>45666</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>46010</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>46054</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>46048</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>45800</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>46052</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>46062</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45485</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>46119</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>46136</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>44984</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45749</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45072</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>46314</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45575</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45190</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>44570</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44512</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>44559</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45351</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44818</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44781</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>44532</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>44516</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44686</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>44495</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44812</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>44841</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>44515</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44524</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44855</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>44502</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44544</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>44544</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44580</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>44789</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>44578</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>44700</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>44700</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>44502</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44538</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44739</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>44536</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44536</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45579</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>44948</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>45091</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>45091</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>45355</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>44496</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>44889</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45232</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44550</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>44498</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>45225</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>46161</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45917</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>46161</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>45915</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>44908</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>44859</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45688</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45917</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>44908</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45639</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>45127</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45391</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45931</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45243</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>45462</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45849</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45883</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45415</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45925</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45925</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45614</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45463</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>44977</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>44631</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44719</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>44998</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>44893</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45085</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>45604</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>46153</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45401</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>45604</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>45772</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44529</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>44894</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45254</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>45385</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>44936</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45621</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>45695</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>45548</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>45714</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45952</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45954</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45595</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>45098</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45958</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>45958</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25946,7 +25946,7 @@
         <v>45957</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>45218</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -26092,7 +26092,7 @@
         <v>45266</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>45126</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>46184</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>45964</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>45961</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>45961</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         <v>45964</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>44531</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>46189</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>46189</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>45616</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>44942</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45965</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45967</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>45232</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>46196</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>46196</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>46196</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>46196</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45439</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45575</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>46121</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>45975</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>44510</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44903</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45979</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>45979</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -28073,7 +28073,7 @@
         <v>45980</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>45159</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>46202</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>45246</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>44930</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45296</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45981</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>45281</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>45385</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>45985</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>44967</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>45187</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>45305</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>44998</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44998</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44834</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>45560</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45560</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>46206</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>45987</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45685</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44970</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>46210</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29772,7 +29772,7 @@
         <v>45992</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29845,7 +29845,7 @@
         <v>45992</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>46210</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>45989</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45995</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>45999</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>45264</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>46258</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45999</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45999</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45999</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>45931</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>46006</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45779</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30794,7 +30794,7 @@
         <v>45786</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>46006</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>46007</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>46007</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45898</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>46007</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>46007</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45786</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45261</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>46279</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>46009</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>46237</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46058</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46239</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>46239</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>46239</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>46070</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>46070</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>46070</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>46070</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>45387</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>44706</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>46239</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>45800</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>45582</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>46282</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32712,7 +32712,7 @@
         <v>46034</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>45595</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>46036</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32931,7 +32931,7 @@
         <v>46237</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>46037</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>44495</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
         <v>46042</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>46288</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>46288</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>46048</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>46288</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -33535,7 +33535,7 @@
         <v>46279</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>46055</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>46058</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45579</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>46290</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45184</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>46294</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>46248</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>44958</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>46066</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>46248</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>46294</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>45485</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>45485</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>45386</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>46072</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>45244</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>46296</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34859,7 +34859,7 @@
         <v>46079</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>45888</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45891</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>45891</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45734</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>45736</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45736</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>45947</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>45888</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>46297</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>46300</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>46255</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>46139</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>46286</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>46289</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>46300</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>46147</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>46302</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>46147</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>45559</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>45849</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>45849</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>46300</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>44984</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45863</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>46304</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>46302</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>45849</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>46128</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>45875</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45875</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45875</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45875</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>45303</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>44911</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>46307</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>44893</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45545</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>46308</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44637</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>44498</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>45945</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>46267</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>45922</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>45968</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>45518</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>46310</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>46268</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>46311</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>46139</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>46139</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>45740</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>46263</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>46269</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>46314</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>46314</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>46314</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>45922</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -39148,7 +39148,7 @@
         <v>45576</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>45999</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>44538</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>46262</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>45586</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>46141</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44928</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>45401</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39737,7 +39737,7 @@
         <v>45996</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45568</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45263</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>46001</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -40034,7 +40034,7 @@
         <v>44910</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -40107,7 +40107,7 @@
         <v>46146</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>46275</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45568</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>46147</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>44637</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -40477,7 +40477,7 @@
         <v>45596</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>44942</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>46156</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>46160</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>44515</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>46160</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45583</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44644</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -41086,7 +41086,7 @@
         <v>44998</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45034</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>45435</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -41305,7 +41305,7 @@
         <v>45159</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45159</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>44998</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>44998</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>45519</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>45595</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41743,7 +41743,7 @@
         <v>45084</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41816,7 +41816,7 @@
         <v>45000</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>44851</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41967,7 +41967,7 @@
         <v>44498</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>44894</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>45244</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>45714</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>44874</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>44946</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>44946</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>45232</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>45548</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42634,7 +42634,7 @@
         <v>44803</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
         <v>45518</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45231</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42853,7 +42853,7 @@
         <v>45134</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42926,7 +42926,7 @@
         <v>44896</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>44498</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -43072,7 +43072,7 @@
         <v>45099</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>44905</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>44552</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>44510</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>44917</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>45159</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45435</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>45254</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>45149</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44946</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44946</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45595</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45616</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45022</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>45699</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45041</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>44998</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45575</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>44628</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44464,7 +44464,7 @@
         <v>45548</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45037</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>44552</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44688,7 +44688,7 @@
         <v>45225</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>44998</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45621</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44912,7 +44912,7 @@
         <v>44531</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44985,7 +44985,7 @@
         <v>45560</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -45058,7 +45058,7 @@
         <v>45560</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>45600</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>45636</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>45685</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>44598</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>45583</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>45261</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44690</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45652,7 +45652,7 @@
         <v>44719</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45219</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45219</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>45150</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45944,7 +45944,7 @@
         <v>45257</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>44854</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -46090,7 +46090,7 @@
         <v>45246</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -46163,7 +46163,7 @@
         <v>44830</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>44935</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46314,7 +46314,7 @@
         <v>45246</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46387,7 +46387,7 @@
         <v>44998</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>44998</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
         <v>44781</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>44540</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46679,7 +46679,7 @@
         <v>44784</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46752,7 +46752,7 @@
         <v>45208</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>45772</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45636</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>44998</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>44496</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>44909</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>44960</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>44917</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47341,7 +47341,7 @@
         <v>45595</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>45376</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>45565</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47570,7 +47570,7 @@
         <v>45376</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45565</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>45006</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>45771</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47872,7 +47872,7 @@
         <v>46000</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47950,7 +47950,7 @@
         <v>45595</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>46111</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
